--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.78830485844301</v>
+      </c>
+      <c r="C2">
         <v>18.69611083213634</v>
-      </c>
-      <c r="C2">
-        <v>30.78830485844301</v>
       </c>
       <c r="D2">
         <v>5.348705990130963</v>
       </c>
       <c r="E2">
-        <v>12.50706352616434</v>
+        <v>20.59633087249196</v>
       </c>
       <c r="F2">
         <v>66.89660560134369</v>
       </c>
       <c r="G2">
-        <v>20.59633087249196</v>
+        <v>12.50706352616434</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.43569115035001</v>
+      </c>
+      <c r="C3">
         <v>16.71716644028837</v>
-      </c>
-      <c r="C3">
-        <v>30.43569115035001</v>
       </c>
       <c r="D3">
         <v>5.981875</v>
       </c>
       <c r="E3">
-        <v>11.36040897472309</v>
+        <v>20.68304458960522</v>
       </c>
       <c r="F3">
         <v>67.95654643567168</v>
       </c>
       <c r="G3">
-        <v>20.68304458960522</v>
+        <v>11.36040897472309</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>44.59279038718292</v>
+      </c>
+      <c r="C4">
         <v>14.41922563417891</v>
-      </c>
-      <c r="C4">
-        <v>44.59279038718292</v>
       </c>
       <c r="D4">
         <v>6.935185185185185</v>
       </c>
       <c r="E4">
-        <v>9.06801007556675</v>
+        <v>28.04366078925273</v>
       </c>
       <c r="F4">
-        <v>62.88832913518051</v>
+        <v>62.88832913518053</v>
       </c>
       <c r="G4">
-        <v>28.04366078925273</v>
+        <v>9.068010075566752</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>35.1756263376558</v>
+      </c>
+      <c r="C5">
         <v>25.63263250660959</v>
-      </c>
-      <c r="C5">
-        <v>35.1756263376558</v>
       </c>
       <c r="D5">
         <v>3.901277013752456</v>
       </c>
       <c r="E5">
+        <v>21.87426602990684</v>
+      </c>
+      <c r="F5">
+        <v>62.18586080012528</v>
+      </c>
+      <c r="G5">
         <v>15.9398731699679</v>
-      </c>
-      <c r="F5">
-        <v>62.18586080012526</v>
-      </c>
-      <c r="G5">
-        <v>21.87426602990683</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.39656055125182</v>
+      </c>
+      <c r="C6">
         <v>16.4594996097258</v>
-      </c>
-      <c r="C6">
-        <v>33.39656055125182</v>
       </c>
       <c r="D6">
         <v>6.075518841466524</v>
       </c>
       <c r="E6">
-        <v>10.98353953256529</v>
+        <v>22.28575909134187</v>
       </c>
       <c r="F6">
         <v>66.73070137609284</v>
       </c>
       <c r="G6">
-        <v>22.28575909134187</v>
+        <v>10.98353953256529</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>40.67796610169492</v>
+      </c>
+      <c r="C7">
         <v>20.33898305084746</v>
-      </c>
-      <c r="C7">
-        <v>40.67796610169492</v>
       </c>
       <c r="D7">
         <v>4.916666666666667</v>
       </c>
       <c r="E7">
-        <v>12.63157894736842</v>
+        <v>25.26315789473684</v>
       </c>
       <c r="F7">
         <v>62.10526315789473</v>
       </c>
       <c r="G7">
-        <v>25.26315789473684</v>
+        <v>12.63157894736842</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>37.17074967765703</v>
+      </c>
+      <c r="C8">
         <v>15.3251059126911</v>
-      </c>
-      <c r="C8">
-        <v>37.17074967765703</v>
       </c>
       <c r="D8">
         <v>6.525240384615385</v>
       </c>
       <c r="E8">
-        <v>10.04952288923783</v>
+        <v>24.3749245077908</v>
       </c>
       <c r="F8">
         <v>65.57555260297137</v>
       </c>
       <c r="G8">
-        <v>24.3749245077908</v>
+        <v>10.04952288923783</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>35.21350429361252</v>
+      </c>
+      <c r="C9">
         <v>25.8087283848959</v>
-      </c>
-      <c r="C9">
-        <v>35.21350429361252</v>
       </c>
       <c r="D9">
         <v>3.874658158614403</v>
       </c>
       <c r="E9">
-        <v>16.02805274500493</v>
+        <v>21.86872191985974</v>
       </c>
       <c r="F9">
         <v>62.10322533513533</v>
       </c>
       <c r="G9">
-        <v>21.86872191985973</v>
+        <v>16.02805274500493</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>33.51737577135434</v>
+      </c>
+      <c r="C10">
         <v>17.11594673595323</v>
-      </c>
-      <c r="C10">
-        <v>33.51737577135434</v>
       </c>
       <c r="D10">
         <v>5.842504743833017</v>
       </c>
       <c r="E10">
-        <v>11.36265631737818</v>
+        <v>22.2509702457956</v>
       </c>
       <c r="F10">
         <v>66.38637343682622</v>
       </c>
       <c r="G10">
-        <v>22.2509702457956</v>
+        <v>11.36265631737818</v>
       </c>
     </row>
   </sheetData>
